--- a/AAII_Financials/Quarterly/ASML_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ASML_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>ASML</t>
   </si>
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44836</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44745</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44654</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44472</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44381</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44290</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44101</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44010</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43919</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43737</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43191</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43009</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42918</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42827</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10637000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10100100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11410200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8788600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9012000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8385500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9589800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8336800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6689000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5707200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7999300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7062900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7535300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7329600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7122100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6244600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5908900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3834800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5404900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5644400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4253400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4454700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4243100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4108000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3628000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2755700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4712100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3658400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3020900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2666400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3717300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3074800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3009000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2563700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2771700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2746000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2357700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2281400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2238900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2130000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4894000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4748700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5459200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4251300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4173600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3858100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4630900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4101700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3247200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2797900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3890500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3399000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3666300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3621300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3454900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3009300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3009700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1956700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2477200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2724400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2090200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2053300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2037700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2155300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1879100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1512100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2447200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2058100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1720700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1556400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2069600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1595200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1705700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1314400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1537900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1568400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1295800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1196100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1181800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1150600</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5742900</v>
+      </c>
+      <c r="E10" s="3">
         <v>5351400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5951000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4537300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4838300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4527400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4958900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4235100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3441800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2909300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4108900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3663800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3869000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3708400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3667200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3235300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2899200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1878100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2927700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2919900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2163200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2401300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2205500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1952700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1748900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1243600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2264900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1600300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1300200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1110100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1647700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1479600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1303200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1249300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1233700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1177500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1062000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1085300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1057200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>979400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,130 +1244,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1456000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1365100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1482100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1296400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1367000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1257700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1155400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1178100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1179300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1113300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1151000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1049300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1091600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1029900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1003800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>885500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>858600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>801500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>737800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>656000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>670600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>636400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>554500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>554200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>618400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>614200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>602300</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>603100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>573400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>565400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>523300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>438900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>417300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>400700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>356100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>352900</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>350800</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>369900</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>337300</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>320900</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1475,8 +1492,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1519,11 +1539,11 @@
       <c r="P14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>50</v>
@@ -1531,11 +1551,11 @@
       <c r="T14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="V14" s="3">
         <v>-231700</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>50</v>
@@ -1552,8 +1572,8 @@
       <c r="AA14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1597,53 +1617,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>281600</v>
+      </c>
+      <c r="E15" s="3">
         <v>298800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>228000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>321100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>298700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>261400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>166900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>263100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>243800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>231300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>142300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>186500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>197800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>185000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1719,8 +1742,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6695300</v>
+      </c>
+      <c r="E17" s="3">
         <v>6462100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7381900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5902200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5890600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5419800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6116000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5611400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4723200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4206100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5355500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4753000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5064700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4933900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4769300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4149700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4109900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2983500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3202900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3577500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2942500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2861600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2743200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2846000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2640700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2273900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3221800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2818600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2439400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2266600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2752100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2169000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2252000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1843200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1993600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2010400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1734100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1653700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1616800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3941700</v>
+      </c>
+      <c r="E18" s="3">
         <v>3638000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4028300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2886300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3121400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2965700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3473900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2725500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1965700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1501100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2643900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2309900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2470500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2395700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2352800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2094900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1799100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>851300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2202000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2066900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1310900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1593100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1499900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1262000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>987400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>481800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1490300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>839900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>581500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>399900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>965100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>905800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>757000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>720500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>778100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>735600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>623600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>627800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>622100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>581700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2048,263 +2081,270 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-120500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-18800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-92300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-104000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-35700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-57500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-86300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-50100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-32600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-40500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-50400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-71900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-44800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-16300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-16900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-10400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-9400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-11800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-14500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-14000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-12100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-16600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>87700</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-39800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4270200</v>
+      </c>
+      <c r="E21" s="3">
         <v>4057400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4275100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3299700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3524100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3262800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3698200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3074900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2259600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1765000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2826600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2546800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2740300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2625500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2552200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2227600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1930400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>976500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2323400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2180700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1419700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1701100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1617000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1379900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1116100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>602500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1628100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>970900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>700900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>515800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1086800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1018700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>864000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>823900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>878400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>835100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>728100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>740400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>830800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>644900</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="3">
         <v>138900</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>50</v>
@@ -2312,23 +2352,23 @@
       <c r="H22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J22" s="3">
         <v>168300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12800</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>168800</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>50</v>
@@ -2336,8 +2376,8 @@
       <c r="P22" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2414,252 +2454,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>4022800</v>
+      </c>
+      <c r="E23" s="3">
         <v>3805600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4060500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3001300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3254500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3054700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3537800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2810900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2003100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1562000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2690100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2367800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2560700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2453700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2349300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2078600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1787300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>834400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2188800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2055600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1580700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1491900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1253300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>979600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>468900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1484600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>833200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>573400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>390400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>956300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>896800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>754500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>708800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>763600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>721600</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>611500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>611200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>709800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>541900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>695300</v>
+      </c>
+      <c r="E24" s="3">
         <v>629700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>726400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>517100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>571100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>503800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>749400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>492600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>312400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>241700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>426200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>363800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>440900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>328800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>395700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>272300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>267900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>124100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>342600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>291700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>216000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>235100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>169800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>172800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>181500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>54800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>145300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>79600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>22500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-20300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>47400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>143500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>118000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>83500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>81600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>96500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>88300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>80500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>94500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>77200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>3327600</v>
+      </c>
+      <c r="E26" s="3">
         <v>3175900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3334000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2484200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2683400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2550900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2788500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2318300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1690700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1320300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2263800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2004000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2119800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2124900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1953600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1806300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1519400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>710200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1846200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1763900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1084500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1345600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1322200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1080500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>798100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>414200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1339300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>753600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>550900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>410800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>908800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>753300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>636500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>625300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>682100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>625100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>523200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>530700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>615300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>464700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>3327600</v>
+      </c>
+      <c r="E27" s="3">
         <v>3175900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3334000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2484200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2683400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2550900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2788500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2318300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1690700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1320300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2263800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2004000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2119800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2124900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2012000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1838800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1535200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>754400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1922500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1874000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1098400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1359100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1347100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1101700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>819300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>441000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1324000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>767800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>560000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>425100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>931500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>753600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>641200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>605500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>663300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>625100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>523200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>530700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>615300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>464700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3146,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3268,8 +3329,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -3512,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E32" s="3">
         <v>120500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>18800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>92300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>104000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>35700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>57500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>86300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>50100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>32600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>40500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>50400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>71900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>44800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>16300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>16900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>10400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>12400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>8000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>8700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>8100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>9400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>8900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>9000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>11800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>14500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>14000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>12100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>16600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-87700</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>39800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>3327600</v>
+      </c>
+      <c r="E33" s="3">
         <v>3175900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3334000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2484200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2683400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2550900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2788500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2318300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1690700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1320300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2263800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2004000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2119800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2124900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2012000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1838800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1535200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>754400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1922500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1874000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1098400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1359100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1347100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1101700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>819300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>441000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1324000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>767800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>560000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>425100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>931500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>753600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>641200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>605500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>663300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>625100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>523200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>530700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>615300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>464700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>3327600</v>
+      </c>
+      <c r="E35" s="3">
         <v>3175900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3334000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2484200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2683400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2550900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2788500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2318300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1690700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1320300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2263800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2004000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2119800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2124900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2012000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1838800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1535200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>754400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1922500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1874000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1098400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1359100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1347100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1101700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>819300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>441000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1324000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>767800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>560000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>425100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>931500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>753600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>641200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>605500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>663300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>625100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>523200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>530700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>615300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>464700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44836</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44745</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44654</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44472</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44381</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44290</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44101</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44010</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43919</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43737</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43191</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43009</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42918</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42827</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4215,1106 +4301,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>7609400</v>
+      </c>
+      <c r="E41" s="3">
         <v>9182500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15165000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5994500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8486800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9855300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13185500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5559100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5157600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5503100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7742600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5266200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6922800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7222600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8050400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3407200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4457400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4691600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7536400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4650800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5487400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3311300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6033700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3665300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3817200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3075300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4123600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1943000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1954100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2695000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3691900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2440300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2553600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2765500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2534600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2331000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2147700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3416500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3412100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3419300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>1037400</v>
+      </c>
+      <c r="E42" s="3">
         <v>467600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>476800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>220000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>329400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>119300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>226900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>332300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>432400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>692200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>147500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>197500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1441000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1298800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>909500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1026800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1567300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>1384300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>592700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>792300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1222600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1080300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>824400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>718400</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>818300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1154900</v>
-      </c>
-      <c r="AL42" s="3">
-        <v>673200</v>
       </c>
       <c r="AM42" s="3">
         <v>673200</v>
       </c>
       <c r="AN42" s="3">
+        <v>673200</v>
+      </c>
+      <c r="AO42" s="3">
         <v>1085800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1349900</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1643300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>9874400</v>
+      </c>
+      <c r="E43" s="3">
         <v>6808800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5423600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7811300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6935700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6009000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5635600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7457100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7042300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6450100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8021200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6752200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6989200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5751700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7582400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>8453300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8202300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6449800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4791900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5525300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5508500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5486700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3199000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4936900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3778000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3768000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3223200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4058400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3257600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3111000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2702800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3223400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2543100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2419100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2391400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2104900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1874600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1583100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1360700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1954900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>13389000</v>
+      </c>
+      <c r="E44" s="3">
         <v>13492200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>13419400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13754400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13562700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11941800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>11276000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12743700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11756500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10642500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9783000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8868000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8443700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8031300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7974400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7439500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6928000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6589700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5614800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5324400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>5381300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4846900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4557500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4788600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5111600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4906300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4446900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4771300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4604500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4503500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4068600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3768800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3532800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3625700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3316200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3364300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>3519600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>3516400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3264200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>3165600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1790900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1827500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>830600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1841800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2303700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2002400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1135100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1993600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2024400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2039600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>888900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2028800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1694900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1871400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1820200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1791300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1662700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1593000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1084600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1236000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1135300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1103700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>799600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>802000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>985600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1022700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>983900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>999800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1032300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>904000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>913900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>722800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>769300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>708000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>572800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>832300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>807400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>692100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>657900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>634300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>33701200</v>
+      </c>
+      <c r="E46" s="3">
         <v>31778600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35947000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29404000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>31295300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29814100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31822500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27759300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26200800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24964600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>26963500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22920900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24056100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22882200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>25546700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21318300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21582800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19756500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19720000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16884000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17710100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16189500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>15888600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15102300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14719200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>14339700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14162000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12365200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>11640800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12436100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12457600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>10979700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>10117200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>10336600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>9969800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>9305700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>9022500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>10293800</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>10044800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>10817500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2635400</v>
+      </c>
+      <c r="E47" s="3">
         <v>2601800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2516500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2731800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1205900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1017000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>934900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1209600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1073900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1026500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1029000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1158200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1135800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1053500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1426600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1662100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1046100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1227700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1382800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1187000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>921600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>928000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1218000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1315600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1457000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1361600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1464000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1907600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1595400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1594500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1408700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1305500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1287400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1305700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1280900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1426900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1259200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>250700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>137600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>9278100</v>
+      </c>
+      <c r="E48" s="3">
         <v>9321100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9668700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9386300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8976000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8143700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7489400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7374800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6902400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6672500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6410700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5708700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5495200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5046700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4582000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4072700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3858500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3620000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3412200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3113500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3105300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2925700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2807900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2590900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2687500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2668500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2712100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2601400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2212300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2117200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2043000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1885000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1879800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1888900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1923700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1741300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1758500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1904400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1980500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1863300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>5905700</v>
+      </c>
+      <c r="E49" s="3">
         <v>5899400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6021700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6015300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6039000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5611100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5393800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5851800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5652000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5717700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5891800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5651100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8899700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5833700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5978800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5863600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5932000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5944700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5970900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5943800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5864700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5685500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5663200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5787800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6108400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6349600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6590600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6938200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6684200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6817900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>6677600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>6257800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>6227200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>6381500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>6403300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>6458000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>6593100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7117500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>7273900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3832500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1747600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1521800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1241200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1074000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>988500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>930700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>818700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>818900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>753000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>699600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>708000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>909400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1087600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1100400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2672200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2534000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2304700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2252600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2287600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2268900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1827100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2056100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1618800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1631800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1543600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1563400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1489300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1544000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1435100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1389700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1233100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1123100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1063600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1006000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>830200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>698900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>745800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>769500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>759700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>777400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>57270500</v>
+      </c>
+      <c r="E54" s="3">
         <v>55369200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>59371400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>52732800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>52547300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>49262100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>50305000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46629600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43652600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>42121700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>44166600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>39705200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>43317800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38187300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>40206300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>35450700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34724100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32801500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32773400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>29397200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>29428800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>27784800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>27196500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>26428500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>26515800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>26282700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>26418000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>25356300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23567900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>24355300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23819900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>21551200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>20575200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>20918600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>20407800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>19630800</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>19379100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>20336000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>20196500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>17375000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -6011,19 +6141,20 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F57" s="3">
         <v>4135000</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>50</v>
@@ -6031,11 +6162,11 @@
       <c r="H57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J57" s="3">
         <v>3624000</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>50</v>
@@ -6043,35 +6174,35 @@
       <c r="L57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N57" s="3">
         <v>2594600</v>
       </c>
-      <c r="N57" s="3" t="s">
+      <c r="O57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3042500</v>
       </c>
-      <c r="P57" s="3" t="s">
+      <c r="Q57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2294300</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>50</v>
@@ -6079,11 +6210,11 @@
       <c r="X57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1374300</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>50</v>
@@ -6091,11 +6222,11 @@
       <c r="AB57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD57" s="3">
         <v>1240000</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>50</v>
@@ -6103,11 +6234,11 @@
       <c r="AF57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AH57" s="3">
         <v>1140300</v>
-      </c>
-      <c r="AH57" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>50</v>
@@ -6115,11 +6246,11 @@
       <c r="AJ57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AK57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL57" s="3">
         <v>939400</v>
-      </c>
-      <c r="AL57" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="AM57" s="3" t="s">
         <v>50</v>
@@ -6127,14 +6258,17 @@
       <c r="AN57" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AO57" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP57" s="3">
         <v>696300</v>
       </c>
-      <c r="AP57" s="3" t="s">
+      <c r="AQ57" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6142,11 +6276,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>2079300</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6154,11 +6288,11 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>1160100</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -6166,17 +6300,17 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>126200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>816500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6186,14 +6320,14 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>551900</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>50</v>
@@ -6201,11 +6335,11 @@
       <c r="X58" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z58" s="3">
         <v>15400</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>50</v>
@@ -6222,8 +6356,8 @@
       <c r="AE58" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -6234,14 +6368,14 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
-      <c r="AJ58" s="3" t="s">
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>28300</v>
-      </c>
-      <c r="AL58" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="AM58" s="3" t="s">
         <v>50</v>
@@ -6249,502 +6383,517 @@
       <c r="AN58" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AO58" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AP58" s="3">
         <v>290700</v>
       </c>
-      <c r="AP58" s="3" t="s">
+      <c r="AQ58" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25267600</v>
+      </c>
+      <c r="E59" s="3">
         <v>23373300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19417400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22480000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21811400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19631600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13352100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17891900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17285200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16235500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13017000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17262400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12639000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18413800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19918600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16933100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15926500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14769900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10486100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9867200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9261800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7019300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5196700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5180100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5052300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5281300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4239900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4547800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4343900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4451300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3345100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3927700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3712100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3514300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2589000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3337000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3506200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3375200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2863800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3840900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>25267600</v>
+      </c>
+      <c r="E60" s="3">
         <v>23373300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28488800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22480000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>21811400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19631600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>20759300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17891900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17285200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16235500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17989100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17262400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>18285500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18413800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19918600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16933100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>15926500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14769900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13332300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9867200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9261800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>7019300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>6586300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5180100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>5052300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5281300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5479900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4547800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4343900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4451300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4485400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3927700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3712100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3514300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3556700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3337000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3506200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3375200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3850800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>3840900</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2263200</v>
+      </c>
+      <c r="E61" s="3">
         <v>3117100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3427900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3162700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4333800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3987200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4083200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5238600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4937500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4975700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5389000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5295000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5281900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4316400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3892300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3785800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4771600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4287600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4417700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4421500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4887900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4730600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4650700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4802100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5045500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4367600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3628700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3883200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3685000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3687300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3580000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3307200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3302500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3342000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3366100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3362300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3360900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3568700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3605700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2806100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>501800</v>
+      </c>
+      <c r="E62" s="3">
         <v>479600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>465200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>484700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>508600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>473000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>461600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>497600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>508300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>477600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>449800</v>
       </c>
-      <c r="N62" s="3" t="s">
+      <c r="O62" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>167000</v>
       </c>
-      <c r="P62" s="3" t="s">
+      <c r="Q62" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6636500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6134800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5703500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4184700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4030000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2721500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2484400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2122500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2130100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2183000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2563600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2491700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2609200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2138300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1957200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1903400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1984300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1962200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1677900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1651200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1417700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1322500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1255500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1368800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1212700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>735000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32378400</v>
+      </c>
+      <c r="E66" s="3">
         <v>31372100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36344300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>30523400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31905000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30305600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31175900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28597200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27890100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>27239700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>29297100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27009500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29063000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27554700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>30447500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26853700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26401700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>23242200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>21780000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17010300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16634100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13872500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13367200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12165100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>12661400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>12140500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>11717800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10569300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9986000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>10042000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10049800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9197100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8692400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8507500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>8316800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8021800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>8122600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>8312700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>8669200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7382100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,19 +7934,22 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F72" s="3">
         <v>20649600</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>50</v>
@@ -7783,11 +7957,11 @@
       <c r="H72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J72" s="3">
         <v>14923200</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>50</v>
@@ -7795,21 +7969,21 @@
       <c r="L72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N72" s="3">
         <v>13683500</v>
       </c>
-      <c r="N72" s="3" t="s">
+      <c r="O72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12050400</v>
       </c>
-      <c r="P72" s="3" t="s">
+      <c r="Q72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
         <v>0</v>
       </c>
@@ -7885,8 +8059,11 @@
       <c r="AP72" s="3">
         <v>0</v>
       </c>
+      <c r="AQ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>24892100</v>
+      </c>
+      <c r="E76" s="3">
         <v>23997100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>23027100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22209400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20642300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18956600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19129100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18032400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15762600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14882000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14869500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12695700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14254800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10632700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9758800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8597100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8322400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9559300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10993400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12386900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12794700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13912400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13829300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>14263300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13854300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14142200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14700300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14787000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13581900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14313400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13770100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12354200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11882800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12411100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12091000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>11609000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>11256500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12023300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11527400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>9992900</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44836</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44745</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44654</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44472</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44381</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44290</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44101</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44010</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43919</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43737</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43191</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43009</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42918</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42827</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>3327600</v>
+      </c>
+      <c r="E81" s="3">
         <v>3175900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3334000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2484200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2683400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2550900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2788500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2318300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1690700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1320300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2263800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2004000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2119800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2124900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2012000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1838800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1535200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>754400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1922500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1874000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1098400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1359100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1347100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1101700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>819300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>441000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1324000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>767800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>560000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>425100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>931500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>753600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>641200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>605500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>663300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>625100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>523200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>530700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>615300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>464700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>298700</v>
+      </c>
+      <c r="E83" s="3">
         <v>261400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>113600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>263100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>243800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>231300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>86100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>186500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>197800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>185000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>47900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>135200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>136800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>144600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>202900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>149000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>143100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>142100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>134600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>125100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>119200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>120400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>125100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>126600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>136500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>133600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>143500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>137700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>127500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>125400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>130600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>121800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>109500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>115100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>114800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>113500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>116600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>129200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>121100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>102900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1942300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2518000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13397100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>653800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>876000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-63500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9881800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1060500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>989400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-271800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3533800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1194000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>420000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>797000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5926200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1263900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2777800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-635900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6956700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1940100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3775900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-961300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4658300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>198300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>405700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-684000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4189000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>85000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>117100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-575100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1928600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>545200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>833500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>214300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1163200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>448800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>595000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-197700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1400700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-3200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-341500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-463600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-525900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-346000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-486000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-449500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-728900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-463200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-568900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-450200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-645500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-531100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-587100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-578000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-465900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-364300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-237500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-251600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-290600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-205000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-255100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-193300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-292100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-220600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-245600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-261400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-356600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-227600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-150900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-175800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-224900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-143000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-137900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-145000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-166400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-107400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-63200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-51400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-113700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-80900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1056500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-561800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1181500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2254200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-501500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-450300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1276400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-240000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-469100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-780700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-681900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1154700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-594900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-474300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-403200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-550000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-157000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-516100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-301100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>1047800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-313100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-953600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-172900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>234300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-501700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1186600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>245400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-409600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-453100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-265000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-62900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>204400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-598400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-847000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>176700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-2931900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-568700</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,68 +10451,69 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1184400</v>
+      </c>
+      <c r="E96" s="3">
         <v>710800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>726900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>724500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>837000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>646900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>618900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>665200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>737500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>616000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>630900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>603700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>727200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>587900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-599300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-587300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-790500</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -10287,11 +10521,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-500300</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10299,17 +10533,17 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-515200</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1040400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -10317,11 +10551,11 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-655600</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
@@ -10340,8 +10574,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2371800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2620900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3068300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-867600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2535200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3413600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-587400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-630800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-827500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1000500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-602500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1488400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-149000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-995300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-950300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1742800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2869800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2202800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3606800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2575800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2764100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1592700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1191300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>9900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>209300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>271000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-731500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-173900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1053600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-57500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-417600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-405300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-928000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-179700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-362000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-172800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-835100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>13900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>1518100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>1738600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>12500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-13900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>8200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>9100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>20800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>9800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-8100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-12300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-30900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>11500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>5900</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-8300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1481000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5697700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9145800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2475400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2173300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3940100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8030400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>185000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-307700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2054100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2243000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1445600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-334500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-674300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4558300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1019900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-247700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2851100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2854500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-934600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2055500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2864000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2511400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>33600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>845900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-913000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2272000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-91900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-696300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1038400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1085800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-135700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-152700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>230900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>203500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>183300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1118000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>4300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-7200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1158400</v>
       </c>
     </row>
